--- a/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,05; 22,23</t>
+          <t>4,41; 21,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,96; 33,66</t>
+          <t>14,45; 33,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 36,27</t>
+          <t>15,49; 36,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 8,23</t>
+          <t>-0,33; 8,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,17; 146,39</t>
+          <t>18,21; 140,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,41; 136,21</t>
+          <t>40,4; 132,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,95; 138,02</t>
+          <t>38,38; 138,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 564,43</t>
+          <t>-24,65; 531,62</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,79; 25,47</t>
+          <t>11,02; 25,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,78; 29,59</t>
+          <t>18,78; 30,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 19,16</t>
+          <t>6,07; 18,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 13,47</t>
+          <t>2,19; 13,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,64; 47,96</t>
+          <t>17,7; 48,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,2; 46,58</t>
+          <t>25,98; 47,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 27,6</t>
+          <t>7,57; 27,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,26; 223,13</t>
+          <t>24,19; 225,54</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 14,57</t>
+          <t>2,84; 14,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,21; 24,71</t>
+          <t>16,84; 25,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 13,15</t>
+          <t>2,4; 13,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 7,35</t>
+          <t>-3,33; 7,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,75; 25,82</t>
+          <t>4,49; 24,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,88; 35,01</t>
+          <t>21,62; 35,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,21; 19,02</t>
+          <t>3,17; 19,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 50,81</t>
+          <t>-15,52; 51,23</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,76; 21,69</t>
+          <t>4,75; 21,38</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,92; 28,12</t>
+          <t>14,56; 28,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 18,04</t>
+          <t>3,13; 18,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,0</t>
+          <t>0,85; 10,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,41; 56,87</t>
+          <t>10,36; 56,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,58; 47,13</t>
+          <t>21,3; 48,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 37,9</t>
+          <t>5,56; 39,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,81; 312,81</t>
+          <t>6,52; 282,21</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 25,95</t>
+          <t>4,76; 25,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,21; 10,89</t>
+          <t>-11,22; 11,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 8,52</t>
+          <t>-14,49; 7,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 4,84</t>
+          <t>-0,31; 4,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 195,12</t>
+          <t>17,86; 192,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,16; 28,83</t>
+          <t>-22,0; 28,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 35,3</t>
+          <t>-37,11; 29,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 112,23</t>
+          <t>-4,54; 111,22</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,64; 12,54</t>
+          <t>3,56; 12,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 8,77</t>
+          <t>-1,39; 9,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,13; 10,25</t>
+          <t>0,14; 10,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 70,69</t>
+          <t>1,93; 68,14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>37,74; 299,9</t>
+          <t>36,88; 289,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 110,18</t>
+          <t>-11,91; 114,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,18; 177,66</t>
+          <t>-0,24; 177,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48,82; 2978,43</t>
+          <t>45,0; 2794,45</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 3,11</t>
+          <t>-7,63; 3,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 8,73</t>
+          <t>-2,44; 8,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 10,74</t>
+          <t>0,8; 10,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,21</t>
+          <t>-2,57; 3,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 47,82</t>
+          <t>-54,14; 45,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 159,9</t>
+          <t>-23,17; 166,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 204,37</t>
+          <t>5,81; 206,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 66,03</t>
+          <t>-29,98; 65,73</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,05</t>
+          <t>6,22; 12,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,28; 15,37</t>
+          <t>9,38; 15,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,95; 10,4</t>
+          <t>4,22; 10,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,41; 24,67</t>
+          <t>3,52; 24,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>14,98; 34,01</t>
+          <t>16,08; 34,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,16; 32,31</t>
+          <t>18,43; 31,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,82; 24,6</t>
+          <t>9,23; 24,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>42,17; 321,31</t>
+          <t>43,21; 380,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,72</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>128,43%</t>
+          <t>125,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 21,54</t>
+          <t>4,54; 21,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,45; 33,16</t>
+          <t>14,85; 33,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,49; 36,22</t>
+          <t>14,71; 36,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 8,31</t>
+          <t>-0,39; 8,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 140,74</t>
+          <t>17,78; 135,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>40,4; 132,29</t>
+          <t>41,59; 137,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,38; 138,42</t>
+          <t>37,16; 138,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 531,62</t>
+          <t>-21,77; 431,62</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>10,29</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>107,88%</t>
+          <t>107,48%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 25,7</t>
+          <t>11,0; 25,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,78; 30,1</t>
+          <t>17,89; 29,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,07; 18,94</t>
+          <t>5,9; 19,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 13,75</t>
+          <t>5,12; 14,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,7; 48,31</t>
+          <t>17,08; 46,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,98; 47,55</t>
+          <t>24,58; 47,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 27,12</t>
+          <t>7,54; 27,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>24,19; 225,54</t>
+          <t>36,75; 195,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>5,0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,84; 14,33</t>
+          <t>3,18; 14,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 25,3</t>
+          <t>16,72; 24,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 13,3</t>
+          <t>2,35; 13,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 7,43</t>
+          <t>0,69; 10,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,49; 24,8</t>
+          <t>5,03; 25,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,62; 35,53</t>
+          <t>21,63; 34,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 19,24</t>
+          <t>3,09; 19,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 51,23</t>
+          <t>3,59; 70,44</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>27,23%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,75; 21,38</t>
+          <t>3,49; 21,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 28,81</t>
+          <t>14,14; 28,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,13; 18,83</t>
+          <t>2,29; 18,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 10,48</t>
+          <t>-0,2; 5,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 56,99</t>
+          <t>7,98; 57,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,3; 48,51</t>
+          <t>20,37; 46,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,56; 39,82</t>
+          <t>3,83; 38,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,52; 282,21</t>
+          <t>-2,23; 66,25</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>44,12%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 25,19</t>
+          <t>4,24; 24,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 11,18</t>
+          <t>-10,56; 11,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 7,66</t>
+          <t>-13,18; 7,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 4,66</t>
+          <t>0,18; 4,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,86; 192,13</t>
+          <t>15,92; 180,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 28,21</t>
+          <t>-20,5; 31,77</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 29,5</t>
+          <t>-35,08; 29,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 111,22</t>
+          <t>1,82; 109,91</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34,33</t>
+          <t>3,16</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>899,4%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,56; 12,28</t>
+          <t>3,95; 12,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 9,14</t>
+          <t>-1,44; 8,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 10,18</t>
+          <t>0,59; 10,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 68,14</t>
+          <t>0,81; 5,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,88; 289,55</t>
+          <t>45,64; 285,17</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 114,95</t>
+          <t>-12,41; 112,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 177,41</t>
+          <t>5,23; 170,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>45,0; 2794,45</t>
+          <t>11,35; 191,02</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 3,24</t>
+          <t>-7,13; 3,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 8,69</t>
+          <t>-1,8; 8,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,8; 10,6</t>
+          <t>0,6; 10,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 3,28</t>
+          <t>-3,03; 3,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 45,34</t>
+          <t>-54,68; 41,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,17; 166,39</t>
+          <t>-17,01; 174,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,81; 206,74</t>
+          <t>3,3; 195,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 65,73</t>
+          <t>-32,98; 68,05</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8,89</t>
+          <t>4,0</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>115,02%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,09</t>
+          <t>6,13; 12,35</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,15</t>
+          <t>9,08; 15,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,22; 10,23</t>
+          <t>3,69; 10,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,52; 24,39</t>
+          <t>2,48; 5,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,08; 34,0</t>
+          <t>15,62; 34,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,43; 31,87</t>
+          <t>17,68; 31,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,23; 24,11</t>
+          <t>8,0; 23,76</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>43,21; 380,66</t>
+          <t>26,03; 68,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados habituales por la persona entrevistada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
